--- a/questions - Template.xlsx
+++ b/questions - Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zander.fias\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51BB3562-804D-46E3-A3D4-66962DF63754}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
   <si>
     <t>type</t>
   </si>
@@ -402,13 +402,31 @@
   </si>
   <si>
     <t>Created from the questions currently hardcoded in the provided index.html file.</t>
+  </si>
+  <si>
+    <t>A colleague asks “Why do I need sustainability training? I work in planning.” What is the best answer?</t>
+  </si>
+  <si>
+    <t> Planning decisions can affect transport, waste, stock and service levels. </t>
+  </si>
+  <si>
+    <t>Planning has nothing to do with sustainability.</t>
+  </si>
+  <si>
+    <t>Only management needs sustainability knowledge.</t>
+  </si>
+  <si>
+    <t>Training is only for audits.</t>
+  </si>
+  <si>
+    <t>Operational decisions influence sustainability outcomes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,17 +439,33 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF2D3D3C"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -468,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -485,9 +519,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -557,8 +593,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Questions_DE" displayName="Questions_DE" ref="A1:I3">
-  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Questions_DE" displayName="Questions_DE" ref="A1:I4">
+  <autoFilter ref="A1:I4" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="question"/>
@@ -859,8 +895,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -870,7 +906,7 @@
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -899,7 +935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -928,7 +964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -955,6 +991,35 @@
       </c>
       <c r="I3" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -968,8 +1033,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -979,7 +1044,7 @@
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1073,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1037,7 +1102,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1064,6 +1129,35 @@
       </c>
       <c r="I3" s="2" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1077,8 +1171,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -1088,7 +1182,7 @@
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1144,6 +1238,35 @@
       </c>
       <c r="I2" s="2" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1157,8 +1280,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -1168,7 +1291,7 @@
     <col min="9" max="9" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,7 +1320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1226,7 +1349,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1253,6 +1376,35 @@
       </c>
       <c r="I3" s="2" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1267,53 +1419,53 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>69</v>
       </c>

--- a/questions - Template.xlsx
+++ b/questions - Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51BB3562-804D-46E3-A3D4-66962DF63754}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77F9C145-0ED5-4337-AB5A-63C57BFCC14A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
   <si>
     <t>type</t>
   </si>
@@ -404,29 +404,32 @@
     <t>Created from the questions currently hardcoded in the provided index.html file.</t>
   </si>
   <si>
-    <t>A colleague asks “Why do I need sustainability training? I work in planning.” What is the best answer?</t>
-  </si>
-  <si>
-    <t> Planning decisions can affect transport, waste, stock and service levels. </t>
-  </si>
-  <si>
-    <t>Planning has nothing to do with sustainability.</t>
-  </si>
-  <si>
-    <t>Only management needs sustainability knowledge.</t>
-  </si>
-  <si>
-    <t>Training is only for audits.</t>
-  </si>
-  <si>
-    <t>Operational decisions influence sustainability outcomes.</t>
+    <t>Quels objectifs correspondent à l’idée « Zero in Focus » ?</t>
+  </si>
+  <si>
+    <t>Choix multiples</t>
+  </si>
+  <si>
+    <t>Zéro émission de CO₂</t>
+  </si>
+  <si>
+    <t>Zéro accident du travail</t>
+  </si>
+  <si>
+    <t>Tolérance zéro envers les comportements contraires à l’éthique</t>
+  </si>
+  <si>
+    <t>Zéro formation</t>
+  </si>
+  <si>
+    <t>Le concept « Zero in Focus » combine les objectifs liés au climat, à la sécurité et à l’intégrité. La formation n’est pas un objectif du programme « Zero ».</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +470,12 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -502,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -521,6 +530,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -575,8 +587,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Questions_FR" displayName="Questions_FR" ref="A1:I2">
-  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Questions_FR" displayName="Questions_FR" ref="A1:I3">
+  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="question"/>
@@ -895,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -991,35 +1003,6 @@
       </c>
       <c r="I3" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1132,33 +1115,15 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>75</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1171,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1240,33 +1205,33 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>75</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1379,33 +1344,15 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>75</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/questions - Template.xlsx
+++ b/questions - Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cafnzholding-my.sharepoint.com/personal/thom_van_dusschoten_synerlogic_nl/Documents/Documenten/GitHub/Sustainability-quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77F9C145-0ED5-4337-AB5A-63C57BFCC14A}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{6B9D40C8-13C7-40B1-9849-545052FB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7254AC0F-27B2-474E-8FC8-95BBE3EEAA21}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
@@ -429,7 +429,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,12 +470,6 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -511,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -530,9 +524,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -587,8 +578,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Questions_FR" displayName="Questions_FR" ref="A1:I3">
-  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Questions_FR" displayName="Questions_FR" ref="A1:I2">
+  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="question"/>
@@ -605,8 +596,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Questions_DE" displayName="Questions_DE" ref="A1:I4">
-  <autoFilter ref="A1:I4" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Questions_DE" displayName="Questions_DE" ref="A1:I3">
+  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="question"/>
@@ -1205,32 +1196,32 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1245,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1343,17 +1334,6 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="7"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
